--- a/Result/profitability/4401.xlsx
+++ b/Result/profitability/4401.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0.225</v>
+        <v>0.25125</v>
       </c>
       <c r="N2" t="n">
-        <v>9.1525</v>
+        <v>9.041250000000002</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>0.21</v>
       </c>
       <c r="M3" t="n">
-        <v>0.22125</v>
+        <v>0.23375</v>
       </c>
       <c r="N3" t="n">
-        <v>9.321250000000001</v>
+        <v>9.27375</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.46</v>
       </c>
       <c r="M4" t="n">
-        <v>0.235</v>
+        <v>0.27</v>
       </c>
       <c r="N4" t="n">
-        <v>9.77</v>
+        <v>9.866250000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.13</v>
       </c>
       <c r="M5" t="n">
-        <v>0.23</v>
+        <v>0.2825</v>
       </c>
       <c r="N5" t="n">
-        <v>10.14875</v>
+        <v>10.17875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2575</v>
+        <v>0.27875</v>
       </c>
       <c r="N6" t="n">
-        <v>10.60875</v>
+        <v>10.68</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.235</v>
+        <v>0.26</v>
       </c>
       <c r="N7" t="n">
-        <v>10.77125</v>
+        <v>10.77875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>0.24</v>
+        <v>0.27625</v>
       </c>
       <c r="N8" t="n">
-        <v>11.105</v>
+        <v>11.15625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4401</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1058</v>
+      </c>
+      <c r="D75" t="n">
+        <v>966</v>
+      </c>
+      <c r="E75" t="n">
+        <v>91</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>38</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.59%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>29</v>
+      </c>
+      <c r="J75" t="n">
+        <v>67</v>
+      </c>
+      <c r="K75" t="n">
+        <v>55</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.24125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8.532500000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.8125</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.4100000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.04987834549878345</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.2400000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.02860548271752084</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
